--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260520_212859.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260520_212859.xlsx
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260520_212859.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260520_212859.xlsx
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
